--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115820470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112636772</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126702838</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115820470</v>
+        <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>103024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1906</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revig blodrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Potentilla anglica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Laichard.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhagen, Sk</t>
+          <t>Hästhagen, 400 m VNV , Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397523</v>
+        <v>397531</v>
       </c>
       <c r="R2" t="n">
-        <v>6199525</v>
+        <v>6199545</v>
       </c>
       <c r="S2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,24 +753,24 @@
           <t>Stehag</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Esv-0047</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Huvudbeståndet på nya koordinater. Enstaka plantor upp till 150 meter norr om punkt längs kant av skogsväg. Exemplar delvis svårbedömda, misstänker vissa vara hybrider Skogsavverkning pågår, flera virkeshögar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,33 +779,38 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
+          <t>Helen Schellenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonny Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Helen Schellenberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115820470</t>
+          <t>https://artportalen.se/Sighting/136092112</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112636772</v>
+        <v>115820470</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,16 +818,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +837,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -881,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,33 +925,33 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112636772</t>
+          <t>https://artportalen.se/Sighting/115820470</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126702838</v>
+        <v>112636772</v>
       </c>
       <c r="B4" t="n">
-        <v>58602</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1005,22 +1008,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,6 +1048,130 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112636772</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126702838</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästhagen, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>397523</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6199525</v>
+      </c>
+      <c r="S5" t="n">
+        <v>23</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stehag</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126702838</t>
         </is>
@@ -1055,6 +1182,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103024</v>
+        <v>103026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103026</v>
+        <v>103027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103027</v>
+        <v>103028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103028</v>
+        <v>103034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103034</v>
+        <v>103035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103035</v>
+        <v>103046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103046</v>
+        <v>103059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103059</v>
+        <v>103060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103060</v>
+        <v>103073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103073</v>
+        <v>103074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
